--- a/procurement_documents/IAR Template.xlsx
+++ b/procurement_documents/IAR Template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\itrac\procurement_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35D3CEF-CDD5-49CF-838F-497EA63AF908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B7176D-5D01-4F81-A7F9-0680C23A1DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{6CD071E1-92CF-4D3E-842E-C4264179AD1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6CD071E1-92CF-4D3E-842E-C4264179AD1A}"/>
   </bookViews>
   <sheets>
     <sheet name="IAR" sheetId="2" r:id="rId1"/>
@@ -579,48 +579,6 @@
   </cellStyleXfs>
   <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -653,9 +611,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -692,15 +647,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -771,6 +717,68 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -780,59 +788,51 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,6 +856,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PAR"/>
@@ -1194,500 +1195,501 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C83917-B674-4037-AFDD-3840452F802F}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:K18099"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="1" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="88"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="29"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="31" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="27"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34" t="s">
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="H16" s="98"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="H16" s="67"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="45"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="45"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="30"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="45"/>
-      <c r="I20" s="98"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="30"/>
+      <c r="I20" s="67"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="45"/>
-      <c r="K21" s="98"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="30"/>
+      <c r="K21" s="67"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="54"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="36"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="59"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="59"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="60"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="60"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="60"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="42"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="60"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="42"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="60"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="42"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="60"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="42"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="60"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="42"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="63"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="45"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="67"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="49"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="67"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="49"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="67"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="49"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="45"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="45"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="30"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="45"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="30"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="77"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="81"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="60"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="81"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83" t="s">
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="85"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="86"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="64"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="17" t="s">
+      <c r="B45" s="12"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="26"/>
-      <c r="F45" s="87"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="65"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="89"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91" t="s">
+      <c r="B47" s="72"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="91" t="s">
+      <c r="E47" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F47" s="18"/>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="89"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17" t="s">
+      <c r="B48" s="72"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="18"/>
+      <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="92"/>
-      <c r="B51" s="93"/>
-      <c r="C51" s="94"/>
-      <c r="D51" s="93" t="s">
+      <c r="A51" s="74"/>
+      <c r="B51" s="75"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="93"/>
-      <c r="F51" s="94"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="76"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="88" t="s">
+      <c r="A52" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="89"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="89" t="s">
+      <c r="B52" s="72"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="E52" s="89"/>
-      <c r="F52" s="90"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="73"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="95"/>
-      <c r="B53" s="96"/>
-      <c r="C53" s="97"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="97"/>
+      <c r="A53" s="68"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="70"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3817,6 +3819,25 @@
     <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="A47:C47"/>
@@ -3825,25 +3846,6 @@
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="D52:F52"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
@@ -3853,534 +3855,535 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7121169-D626-4954-A0C3-D0B109C5A29F}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:K18099"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="88"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="31" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34" t="s">
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39" t="s">
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="24" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="H16" s="98"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="H16" s="67"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="45"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="45"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="30"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="45"/>
-      <c r="I20" s="98"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="30"/>
+      <c r="I20" s="67"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="45"/>
-      <c r="K21" s="98"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="30"/>
+      <c r="K21" s="67"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="54"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="36"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="59"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="59"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="60"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="60"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="60"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="42"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="60"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="42"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="60"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="42"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="60"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="42"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="60"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="42"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="63"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="45"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="67"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="49"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="67"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="49"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="67"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="49"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="45"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="45"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="30"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="45"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="30"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="77"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="81"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="60"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="81"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83" t="s">
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="85"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="86"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="64"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="26" t="s">
+      <c r="B45" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="17" t="s">
+      <c r="C45" s="4"/>
+      <c r="D45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E45" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="87"/>
+      <c r="F45" s="65"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="89"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91" t="s">
+      <c r="B47" s="72"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="91" t="s">
+      <c r="E47" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F47" s="18"/>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="89"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17" t="s">
+      <c r="B48" s="72"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="18"/>
+      <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="93"/>
-      <c r="C51" s="94"/>
-      <c r="D51" s="93" t="s">
+      <c r="B51" s="75"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="93"/>
-      <c r="F51" s="94"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="76"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="88" t="s">
+      <c r="A52" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="89"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="89" t="s">
+      <c r="B52" s="72"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="E52" s="89"/>
-      <c r="F52" s="90"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="73"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="95"/>
-      <c r="B53" s="96"/>
-      <c r="C53" s="97"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="97"/>
+      <c r="A53" s="68"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="70"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6510,6 +6513,25 @@
     <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="A47:C47"/>
@@ -6518,25 +6540,6 @@
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="D52:F52"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>

--- a/procurement_documents/IAR Template.xlsx
+++ b/procurement_documents/IAR Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\itrac\procurement_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B7176D-5D01-4F81-A7F9-0680C23A1DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1882B32E-5EC8-443C-B214-EA64B92EAF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6CD071E1-92CF-4D3E-842E-C4264179AD1A}"/>
   </bookViews>
@@ -45,8 +45,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>TECHNOLOGICAL UNIVERSITY OF THE PHILIPPINES</t>
   </si>
@@ -196,6 +218,13 @@
   </si>
   <si>
     <t>iar_supplier</t>
+  </si>
+  <si>
+    <t>The Technological University of the Philippines shall be a premiere state university with recognized excellence in engineering and technology education at par with the leading universities in the ASEAN region</t>
+  </si>
+  <si>
+    <t>TECHNOLOGICAL UNIVERSITY OF THE PHILIPPINES
+                          TAGUIG CITY</t>
   </si>
 </sst>
 </file>
@@ -577,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -740,6 +769,72 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -767,71 +862,68 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -876,6 +968,70 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1206,69 +1362,65 @@
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="112" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B2" s="105" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="106"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="94" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="95" t="s">
+      <c r="A3" s="109"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="96" t="s">
+      <c r="A4" s="109"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="98"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="75"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="88"/>
+      <c r="A5" s="109"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="79"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="89" t="s">
+      <c r="A6" s="109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
+      <c r="A7" s="113"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1332,11 +1484,11 @@
       <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
@@ -1345,12 +1497,2697 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
+      <c r="A14" s="116"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="116"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="116"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="H16" s="67"/>
+    </row>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="116"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+    </row>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="116"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="30"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="116"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="117"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="30"/>
+      <c r="I20" s="67"/>
+    </row>
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="117"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="30"/>
+      <c r="K21" s="67"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="117"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="36"/>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="117"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="116"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+    </row>
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="116"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="119"/>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="116"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="119"/>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="116"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="42"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="116"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="42"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="116"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="42"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="116"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="42"/>
+    </row>
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="116"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="42"/>
+    </row>
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="116"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="42"/>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="116"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="42"/>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="116"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="45"/>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="116"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="49"/>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="116"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="49"/>
+    </row>
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="116"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="49"/>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="116"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="116"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="116"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="116"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="60"/>
+    </row>
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="116"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="64"/>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="F45" s="65"/>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="94"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="94"/>
+      <c r="C48" s="95"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="96"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="97"/>
+      <c r="F51" s="98"/>
+    </row>
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="94"/>
+      <c r="C52" s="95"/>
+      <c r="D52" s="94" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="94"/>
+      <c r="F52" s="95"/>
+    </row>
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="90"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="91"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="92"/>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1062" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1063" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1064" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1065" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1066" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1067" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1115" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1116" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1117" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1118" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1119" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1120" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1168" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1169" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1170" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1221" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1222" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1223" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1225" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1273" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1274" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1275" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1276" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1278" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1327" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1328" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1346" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1375" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1376" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1377" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1378" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1380" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1396" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1429" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1430" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1431" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1432" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1433" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1434" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1483" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1484" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1485" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1487" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1536" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1537" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1538" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1539" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1540" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1541" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1590" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1591" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1592" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1593" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1594" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1643" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1644" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1645" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1646" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1648" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1698" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1699" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1700" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1702" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1751" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1752" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1753" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1754" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1755" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1756" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1805" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1806" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1807" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1808" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1809" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1810" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1859" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1860" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1861" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1862" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1863" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1864" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1912" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1913" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1914" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1915" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1916" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1917" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1964" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1965" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1966" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1967" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1968" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1969" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2018" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2019" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2020" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2022" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2071" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2072" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2073" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2074" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2124" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2125" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2127" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2177" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2178" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2180" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2181" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2230" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2231" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2232" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2283" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2284" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2285" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2286" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2335" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2336" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2337" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2338" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2339" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2388" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2389" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2390" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2392" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2393" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2441" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2442" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2443" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2445" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2446" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2494" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2495" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2496" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2498" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2499" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2547" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2548" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2549" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2550" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2551" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2552" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2601" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2602" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2603" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2604" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2605" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2655" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2656" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2657" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2658" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2660" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2708" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2709" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2710" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2711" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2712" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2713" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2761" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2762" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2763" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2764" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2765" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2814" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2815" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2816" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2817" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2818" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2868" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2869" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2871" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2976" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2978" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2981" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3030" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3031" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3032" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3034" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3035" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3084" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3085" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3086" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3088" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3089" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3139" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3191" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3192" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3193" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3195" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3196" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3244" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3245" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3247" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3298" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3299" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3301" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3351" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3352" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3353" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3354" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3355" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3405" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3406" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3407" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3409" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3458" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3459" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3460" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3462" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3511" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3512" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3513" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3514" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3564" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3565" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3566" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3567" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3568" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3618" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3619" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3620" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3621" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3622" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3671" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3672" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3673" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3674" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3675" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3724" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3725" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3726" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3727" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3728" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3729" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3778" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3779" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3780" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3781" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3782" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3783" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3831" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3832" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3833" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3834" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3835" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3836" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3884" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3885" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3886" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3887" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3888" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3889" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3939" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3940" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3941" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3942" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3943" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3991" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3992" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3993" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3995" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3996" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4044" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4045" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4046" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4048" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4049" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4097" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4098" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4099" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4101" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4102" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4152" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4153" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4154" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4155" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4204" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4205" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4206" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4207" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4208" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4209" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4257" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4258" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4259" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4260" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4261" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4262" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4310" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4311" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4312" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4313" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4314" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4315" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4364" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4365" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4366" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4367" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4368" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4369" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4417" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4418" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4419" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4420" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4421" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4422" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4471" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4472" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4473" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4474" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4475" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4476" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4525" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4526" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4527" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4528" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4529" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4530" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4578" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4579" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4580" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4582" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4583" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4631" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4632" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4633" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4634" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4636" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4685" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4686" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4687" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4688" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4689" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4690" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4739" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4740" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4741" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4742" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4743" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4744" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4793" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4794" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4795" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4796" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4797" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4846" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4847" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4848" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4849" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4850" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4899" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4900" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4901" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4902" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4903" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4953" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4954" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4955" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4956" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4957" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5007" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5008" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5009" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5010" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5011" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5060" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5061" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5062" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5063" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5064" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5114" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5115" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5116" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5117" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5167" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5168" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5219" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5220" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5221" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5222" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5223" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5272" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5273" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5274" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5275" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5276" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5327" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5328" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5378" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5379" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5380" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5381" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5382" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5383" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5433" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5434" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5435" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5436" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5437" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5487" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5489" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5490" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5539" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5540" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5541" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5542" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5543" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5544" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5593" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5594" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5595" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5596" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5597" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5598" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5648" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5649" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5650" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5651" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5652" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5702" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5703" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5704" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5705" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5706" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5754" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5755" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5756" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5757" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5758" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5759" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5808" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5809" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5810" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5811" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5812" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5813" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5861" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5862" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5863" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5864" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5865" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5866" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5914" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5915" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5916" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5917" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5918" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5919" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5967" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5968" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5969" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5970" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5971" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5972" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6022" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6023" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6024" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6025" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6026" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6076" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6077" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6078" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6079" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6080" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6129" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6130" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6131" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6132" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6181" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6182" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6183" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6184" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6185" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6186" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6235" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6236" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6237" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6238" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6239" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6288" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6289" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6290" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6291" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6292" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6341" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6342" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6343" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6345" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6394" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6395" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6396" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6397" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6398" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6399" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6448" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6449" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6450" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6451" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6452" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6453" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6502" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6503" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6504" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6505" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6506" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6507" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6556" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6557" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6558" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6559" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6560" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6561" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6609" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6610" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6611" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6612" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6613" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6614" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6662" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6663" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6664" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6665" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6666" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6667" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6716" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6717" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6718" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6719" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6720" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6721" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6769" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6770" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6771" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6772" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6773" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6774" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6823" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6824" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6825" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6826" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6827" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6828" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6877" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6878" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6879" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6880" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6881" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6882" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6931" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6932" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6933" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6934" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6935" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6936" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6984" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6985" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6986" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6987" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6988" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6989" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7037" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7038" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7039" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7040" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7041" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7042" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7090" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7091" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7092" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7093" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7094" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7095" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7143" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7144" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7145" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7146" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7148" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7197" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7198" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7199" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7200" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7201" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7202" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7250" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7251" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7252" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7253" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7254" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7255" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7304" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7305" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7306" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7307" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7308" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7357" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7358" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7359" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7360" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7361" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7411" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7412" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7413" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7414" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7415" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7464" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7517" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7518" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7519" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7521" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7570" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7572" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7575" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7677" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7679" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7730" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7731" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7732" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7733" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7735" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7783" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7784" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7785" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7786" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7787" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7788" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7836" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7837" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7838" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7840" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7841" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7890" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7891" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7892" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7894" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7895" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7943" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7944" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7945" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7946" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7947" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7948" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7996" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7997" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7998" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7999" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8000" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8008" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8050" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8051" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8052" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8053" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8054" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8055" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8104" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8105" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8106" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8107" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8108" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8157" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8158" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8159" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8160" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8210" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8211" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8212" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8213" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8214" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8215" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8264" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8265" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8266" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8267" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8268" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8269" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8317" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8318" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8319" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8320" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8321" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8322" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8370" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8371" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8372" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8373" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8374" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8375" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8424" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8425" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8426" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8427" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8428" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8477" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8478" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8479" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8480" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8481" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8482" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8530" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8531" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8532" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8533" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8534" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8535" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8583" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8584" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8585" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8587" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8588" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8609" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8611" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8617" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8637" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8638" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8639" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8640" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8641" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8642" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8668" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8691" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8692" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8693" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8694" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8695" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8696" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8744" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8745" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8746" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8747" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8748" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8749" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8800" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8801" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8853" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8854" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8905" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8906" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8907" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8958" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8959" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8960" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8961" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8962" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9011" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9012" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9013" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9015" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9016" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9066" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9067" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9068" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9069" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9119" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9120" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9173" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9174" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9177" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9226" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9227" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9228" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9230" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9231" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9279" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9280" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9281" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9283" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9284" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9333" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9334" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9335" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9336" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9337" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9338" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9386" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9387" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9388" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9389" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9390" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9440" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9441" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9442" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9443" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9445" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9494" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9495" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9496" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9498" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9499" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9548" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9549" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9550" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9551" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9552" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9553" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9601" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9602" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9603" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9604" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9605" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9654" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9655" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9656" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9657" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9658" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9707" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9708" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9709" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9710" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9711" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9712" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9761" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9762" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9763" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9764" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9765" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9814" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9815" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9816" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9817" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9818" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9868" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9869" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9871" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9975" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9976" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9978" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10028" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10029" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10030" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10031" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10032" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10082" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10083" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10084" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10085" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10086" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10136" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10137" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10139" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10189" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10190" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10191" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10192" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10193" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10244" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10245" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10247" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10298" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10299" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10301" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10351" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10352" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10353" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10354" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10355" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10404" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10405" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10406" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10407" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10409" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10458" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10459" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10460" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10462" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10511" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10512" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10513" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10514" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10564" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10565" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10566" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10567" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10568" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10617" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10618" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10619" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10620" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10621" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10622" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10670" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10671" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10672" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10673" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10674" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10675" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10723" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10724" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10725" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10726" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10727" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10728" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10776" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10777" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10778" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10779" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10780" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10781" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10829" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10830" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10831" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10832" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10833" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10834" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10882" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10883" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10884" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10885" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10886" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10887" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10935" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10936" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10937" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10939" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10940" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10989" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10990" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10991" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10992" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10993" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11042" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11043" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11044" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11045" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11046" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11095" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11096" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11097" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11098" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11148" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11149" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11150" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11152" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11199" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11200" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11201" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11202" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11203" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11204" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11252" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11253" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11254" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11255" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11256" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11257" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11305" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11306" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11307" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11308" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11309" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11310" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11358" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11359" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11360" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11361" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11362" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11363" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11411" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11412" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11413" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11414" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11415" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11416" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11464" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11466" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11469" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11517" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11518" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11519" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11521" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11522" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11570" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11572" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11575" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11677" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11679" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11729" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11730" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11731" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11732" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11733" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11782" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11783" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11784" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11785" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11786" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11787" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11835" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11836" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11837" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11838" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11840" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11888" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11889" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11890" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11891" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11892" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11941" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11942" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11943" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11944" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11945" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11946" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11995" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11996" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11997" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11998" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11999" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12048" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12049" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12050" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12051" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12052" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12101" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12102" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12104" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12153" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12154" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12155" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12157" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12158" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12206" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12207" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12208" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12209" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12210" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12211" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12259" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12260" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12261" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12262" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12263" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12264" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12312" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12313" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12314" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12315" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12316" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12317" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12365" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12366" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12367" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12368" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12369" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12370" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12418" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12419" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12420" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12421" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12422" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12471" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12472" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12473" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12474" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12475" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12476" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12524" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12525" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12526" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12527" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12528" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12529" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12577" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12578" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12579" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12580" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12582" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12630" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12631" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12632" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12633" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12634" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12683" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12684" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12685" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12686" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12687" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12688" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12736" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12737" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12738" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12739" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12740" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12741" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12789" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12790" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12791" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12792" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12793" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12794" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12842" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12843" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12844" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12845" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12846" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12847" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12895" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12896" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12897" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12899" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12900" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12948" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12949" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12950" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12951" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12953" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13002" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13003" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13004" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13005" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13066" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13067" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13068" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13069" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13119" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13120" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13172" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13173" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13225" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13226" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13227" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13228" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13278" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13279" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13280" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13281" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13339" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13340" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13341" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13342" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13343" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13401" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13402" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13403" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13404" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13405" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13406" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13464" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13522" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13523" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13524" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13525" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13526" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13527" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13582" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13583" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13584" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13585" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13636" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13637" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13638" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13639" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13640" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13689" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13690" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13691" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13692" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13693" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13694" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13743" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13744" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13745" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13746" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13747" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13748" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13797" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13798" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13800" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13801" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13853" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13854" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13905" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13906" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13907" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13910" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13959" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13960" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13961" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13962" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13964" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14013" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14014" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14015" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14016" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14018" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14067" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14068" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14069" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14071" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14072" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14122" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14123" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14124" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14176" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14177" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14178" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14180" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14230" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14231" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14232" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14283" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14284" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14285" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14286" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14288" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14337" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14338" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14339" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14341" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14342" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14392" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14393" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14394" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14395" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14396" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14445" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14446" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14447" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14448" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14449" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14498" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14499" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14500" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14501" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14502" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14550" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14551" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14552" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14553" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14554" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14555" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14603" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14604" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14605" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14607" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14608" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14656" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14657" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14658" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14660" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14661" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14710" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14711" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14712" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14713" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14714" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14715" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14763" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14764" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14765" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14767" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14768" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14816" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14817" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14818" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14820" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14821" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14869" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14871" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14874" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14975" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14976" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14978" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15029" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15030" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15031" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15032" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15034" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15083" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15084" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15085" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15086" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15088" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15139" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15191" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15192" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15193" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15195" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15196" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15245" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15247" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15250" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15299" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15301" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15304" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15353" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15354" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15355" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15357" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15358" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15407" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15408" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15409" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15411" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15412" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15462" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15463" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15464" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15465" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15516" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15517" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15518" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15519" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15570" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15572" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15677" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15679" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15682" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15731" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15732" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15733" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15735" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15736" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15785" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15786" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15787" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15788" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15789" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15790" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15840" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15841" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15842" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15843" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15844" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15894" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15895" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15896" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15897" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15947" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15948" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15949" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15950" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15951" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16002" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16003" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16004" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16005" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16055" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16056" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16057" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16058" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16059" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16060" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16109" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16110" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16111" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16112" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16114" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16163" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16164" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16165" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16217" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16218" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16219" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16221" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16222" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16271" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16272" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16273" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16274" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16275" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16276" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16327" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16328" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16380" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16381" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16382" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16383" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16384" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16433" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16434" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16435" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16436" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16437" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16487" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16489" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16490" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16538" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16539" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16540" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16541" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16542" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16543" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16591" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16592" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16593" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16594" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16596" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16644" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16645" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16646" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16648" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16649" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16698" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16699" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16700" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16702" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16750" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16751" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16752" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16753" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16754" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16755" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16804" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16805" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16806" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16807" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16808" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16857" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16858" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16859" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16860" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16861" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16910" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16911" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16912" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16913" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16914" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16964" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16965" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16966" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16967" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16968" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17018" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17019" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17020" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17022" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17071" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17072" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17073" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17074" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17076" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17126" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17127" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17129" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17130" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17180" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17181" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17182" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17183" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17184" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17234" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17235" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17236" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17237" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17238" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17288" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17289" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17290" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17291" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17292" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17341" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17342" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17343" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17345" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17346" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17395" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17396" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17397" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17398" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17399" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17400" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17449" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17450" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17451" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17452" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17453" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17454" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17503" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17504" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17505" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17506" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17507" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17508" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17557" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17558" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17559" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17560" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17561" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17562" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17611" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17612" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17613" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17614" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17615" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17616" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17665" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17666" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17667" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17668" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17669" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17670" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17719" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17720" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17721" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17722" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17723" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17724" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17773" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17774" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17775" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17776" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17777" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17778" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17826" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17827" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17828" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17829" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17830" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17831" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17880" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17881" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17882" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17883" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17884" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17885" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17934" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17935" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17936" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17937" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17939" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17988" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17989" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17990" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17991" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17992" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17993" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18041" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18042" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18043" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18044" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18045" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18046" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18094" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18095" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18096" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18097" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18098" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:C7"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="B2:C5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7121169-D626-4954-A0C3-D0B109C5A29F}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A2:K18099"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+    </row>
+    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="74"/>
+      <c r="F4" s="75"/>
+    </row>
+    <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="79"/>
+    </row>
+    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
@@ -1395,9 +4232,9 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
       <c r="E20" s="24"/>
       <c r="F20" s="30"/>
       <c r="I20" s="67"/>
@@ -1413,9 +4250,9 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="80"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="86"/>
       <c r="E22" s="24"/>
       <c r="F22" s="36"/>
     </row>
@@ -1509,9 +4346,9 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="80"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="86"/>
       <c r="E34" s="24"/>
       <c r="F34" s="45"/>
     </row>
@@ -1565,9 +4402,9 @@
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="83"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="89"/>
       <c r="E41" s="59"/>
       <c r="F41" s="60"/>
     </row>
@@ -1580,16 +4417,16 @@
       <c r="F42" s="60"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="84" t="s">
+      <c r="A43" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84" t="s">
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="62"/>
@@ -1603,12 +4440,16 @@
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="12"/>
+      <c r="B45" s="12" t="s">
+        <v>41</v>
+      </c>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="12"/>
+      <c r="E45" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="F45" s="65"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1620,11 +4461,11 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="71" t="s">
+      <c r="A47" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="73"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="95"/>
       <c r="D47" s="66" t="s">
         <v>25</v>
       </c>
@@ -1634,11 +4475,11 @@
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="71" t="s">
+      <c r="A48" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="73"/>
+      <c r="B48" s="94"/>
+      <c r="C48" s="95"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="s">
         <v>28</v>
@@ -1662,34 +4503,36 @@
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="74"/>
-      <c r="B51" s="75"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" s="75"/>
-      <c r="F51" s="76"/>
+      <c r="A51" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="97"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="97"/>
+      <c r="F51" s="98"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="71" t="s">
+      <c r="A52" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="72"/>
-      <c r="C52" s="73"/>
-      <c r="D52" s="72" t="s">
+      <c r="B52" s="94"/>
+      <c r="C52" s="95"/>
+      <c r="D52" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="E52" s="72"/>
-      <c r="F52" s="73"/>
+      <c r="E52" s="94"/>
+      <c r="F52" s="95"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="68"/>
-      <c r="B53" s="69"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="69"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="70"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="91"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="92"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3819,12 +6662,14 @@
     <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A5:C5"/>
@@ -3838,2708 +6683,12 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7121169-D626-4954-A0C3-D0B109C5A29F}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:K18099"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-    </row>
-    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="94" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="95" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="96" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="98"/>
-    </row>
-    <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="88"/>
-    </row>
-    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="89" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="H16" s="67"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="30"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="30"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="30"/>
-      <c r="I20" s="67"/>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="30"/>
-      <c r="K21" s="67"/>
-    </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="36"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="41"/>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="41"/>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="42"/>
-    </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="42"/>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="42"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="42"/>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="42"/>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="42"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="42"/>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="45"/>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="49"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="49"/>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="49"/>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="30"/>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="30"/>
-    </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="20"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="30"/>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="60"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="60"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="62"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="64"/>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F45" s="65"/>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="4"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="73"/>
-      <c r="D47" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="4"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="4"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="4"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="75"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="75"/>
-      <c r="F51" s="76"/>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" s="72"/>
-      <c r="C52" s="73"/>
-      <c r="D52" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="72"/>
-      <c r="F52" s="73"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="68"/>
-      <c r="B53" s="69"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="69"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="70"/>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1009" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1012" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1013" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1062" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1063" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1064" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1065" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1066" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1067" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1115" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1116" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1117" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1118" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1119" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1120" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1168" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1169" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1170" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1221" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1222" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1223" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1225" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1273" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1274" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1275" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1276" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1278" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1327" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1328" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1346" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1375" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1376" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1377" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1378" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1380" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1396" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1429" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1430" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1431" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1432" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1433" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1434" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1483" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1484" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1485" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1487" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1536" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1537" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1538" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1539" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1540" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1541" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1590" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1591" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1592" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1593" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1594" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1643" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1644" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1645" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1646" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1648" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1698" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1699" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1700" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1702" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1751" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1752" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1753" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1754" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1755" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1756" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1805" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1806" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1807" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1808" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1809" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1810" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1859" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1860" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1861" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1862" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1863" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1864" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1912" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1913" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1914" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1915" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1916" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1917" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1964" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1965" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1966" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1967" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1968" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1969" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2018" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2019" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2020" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2022" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2071" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2072" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2073" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2074" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2124" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2125" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2127" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2177" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2178" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2180" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2181" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2230" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2231" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2232" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2283" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2284" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2285" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2286" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2335" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2336" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2337" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2338" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2339" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2388" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2389" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2390" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2392" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2393" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2441" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2442" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2443" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2445" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2446" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2494" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2495" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2496" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2498" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2499" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2547" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2548" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2549" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2550" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2551" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2552" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2601" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2602" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2603" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2604" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2605" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2655" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2656" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2657" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2658" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2660" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2708" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2709" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2710" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2711" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2712" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2713" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2761" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2762" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2763" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2764" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2765" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2814" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2815" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2816" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2817" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2818" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2868" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2869" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2871" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2976" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2978" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2981" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3030" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3031" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3032" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3034" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3035" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3084" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3085" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3086" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3088" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3089" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3139" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3191" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3192" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3193" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3195" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3196" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3244" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3245" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3247" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3298" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3299" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3301" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3351" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3352" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3353" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3354" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3355" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3405" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3406" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3407" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3409" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3458" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3459" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3460" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3462" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3511" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3512" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3513" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3514" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3564" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3565" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3566" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3567" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3568" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3618" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3619" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3620" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3621" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3622" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3671" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3672" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3673" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3674" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3675" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3724" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3725" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3726" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3727" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3728" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3729" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3778" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3779" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3780" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3781" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3782" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3783" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3831" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3832" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3833" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3834" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3835" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3836" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3884" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3885" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3886" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3887" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3888" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3889" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3939" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3940" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3941" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3942" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3943" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3991" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3992" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3993" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3995" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3996" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4044" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4045" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4046" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4048" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4049" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4097" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4098" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4099" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4101" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4102" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4152" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4153" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4154" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4155" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4204" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4205" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4206" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4207" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4208" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4209" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4257" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4258" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4259" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4260" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4261" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4262" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4310" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4311" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4312" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4313" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4314" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4315" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4364" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4365" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4366" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4367" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4368" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4369" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4417" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4418" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4419" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4420" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4421" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4422" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4471" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4472" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4473" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4474" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4475" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4476" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4525" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4526" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4527" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4528" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4529" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4530" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4578" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4579" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4580" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4582" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4583" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4631" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4632" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4633" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4634" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4636" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4685" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4686" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4687" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4688" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4689" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4690" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4739" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4740" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4741" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4742" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4743" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4744" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4793" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4794" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4795" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4796" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4797" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4846" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4847" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4848" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4849" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4850" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4899" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4900" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4901" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4902" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4903" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4953" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4954" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4955" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4956" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4957" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5007" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5008" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5009" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5010" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5011" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5060" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5061" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5062" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5063" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5064" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5114" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5115" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5116" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5117" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5167" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5168" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5219" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5220" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5221" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5222" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5223" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5272" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5273" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5274" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5275" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5276" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5327" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5328" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5378" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5379" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5380" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5381" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5382" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5383" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5433" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5434" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5435" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5436" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5437" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5487" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5489" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5490" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5539" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5540" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5541" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5542" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5543" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5544" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5593" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5594" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5595" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5596" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5597" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5598" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5648" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5649" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5650" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5651" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5652" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5702" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5703" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5704" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5705" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5706" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5754" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5755" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5756" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5757" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5758" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5759" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5808" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5809" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5810" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5811" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5812" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5813" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5861" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5862" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5863" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5864" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5865" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5866" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5914" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5915" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5916" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5917" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5918" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5919" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5967" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5968" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5969" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5970" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5971" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5972" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6022" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6023" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6024" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6025" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6026" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6076" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6077" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6078" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6079" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6080" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6129" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6130" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6131" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6132" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6181" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6182" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6183" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6184" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6185" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6186" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6235" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6236" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6237" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6238" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6239" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6288" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6289" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6290" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6291" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6292" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6341" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6342" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6343" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6345" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6394" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6395" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6396" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6397" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6398" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6399" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6448" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6449" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6450" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6451" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6452" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6453" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6502" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6503" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6504" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6505" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6506" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6507" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6556" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6557" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6558" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6559" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6560" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6561" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6609" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6610" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6611" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6612" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6613" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6614" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6662" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6663" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6664" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6665" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6666" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6667" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6716" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6717" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6718" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6719" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6720" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6721" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6769" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6770" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6771" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6772" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6773" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6774" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6823" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6824" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6825" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6826" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6827" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6828" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6877" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6878" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6879" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6880" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6881" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6882" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6931" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6932" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6933" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6934" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6935" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6936" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6984" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6985" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6986" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6987" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6988" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6989" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7037" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7038" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7039" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7040" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7041" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7042" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7090" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7091" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7092" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7093" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7094" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7095" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7143" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7144" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7145" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7146" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7148" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7197" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7198" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7199" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7200" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7201" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7202" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7250" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7251" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7252" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7253" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7254" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7255" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7304" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7305" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7306" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7307" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7308" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7357" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7358" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7359" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7360" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7361" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7411" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7412" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7413" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7414" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7415" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7464" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7517" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7518" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7519" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7521" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7570" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7572" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7575" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7677" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7679" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7730" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7731" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7732" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7733" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7735" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7783" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7784" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7785" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7786" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7787" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7788" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7836" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7837" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7838" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7840" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7841" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7890" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7891" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7892" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7894" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7895" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7943" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7944" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7945" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7946" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7947" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7948" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7996" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7997" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7998" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7999" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8000" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8008" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8050" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8051" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8052" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8053" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8054" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8055" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8104" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8105" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8106" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8107" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8108" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8157" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8158" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8159" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8160" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8210" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8211" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8212" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8213" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8214" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8215" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8264" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8265" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8266" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8267" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8268" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8269" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8317" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8318" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8319" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8320" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8321" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8322" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8370" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8371" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8372" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8373" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8374" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8375" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8424" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8425" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8426" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8427" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8428" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8477" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8478" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8479" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8480" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8481" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8482" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8530" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8531" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8532" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8533" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8534" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8535" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8583" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8584" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8585" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8587" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8588" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8609" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8611" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8617" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8637" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8638" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8639" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8640" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8641" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8642" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8668" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8691" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8692" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8693" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8694" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8695" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8696" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8744" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8745" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8746" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8747" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8748" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8749" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8798" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8800" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8801" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8853" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8854" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8904" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8905" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8906" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8907" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8958" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8959" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8960" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8961" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8962" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9011" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9012" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9013" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9014" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9015" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9016" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9066" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9067" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9068" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9069" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9119" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9120" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9173" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9174" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9177" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9226" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9227" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9228" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9230" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9231" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9279" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9280" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9281" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9283" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9284" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9333" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9334" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9335" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9336" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9337" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9338" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9386" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9387" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9388" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9389" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9390" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9440" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9441" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9442" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9443" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9445" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9494" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9495" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9496" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9498" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9499" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9548" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9549" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9550" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9551" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9552" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9553" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9601" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9602" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9603" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9604" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9605" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9654" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9655" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9656" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9657" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9658" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9707" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9708" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9709" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9710" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9711" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9712" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9761" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9762" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9763" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9764" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9765" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9814" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9815" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9816" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9817" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9818" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9868" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9869" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9871" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9975" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9976" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9978" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10028" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10029" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10030" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10031" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10032" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10082" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10083" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10084" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10085" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10086" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10136" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10137" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10139" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10189" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10190" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10191" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10192" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10193" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10244" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10245" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10247" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10298" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10299" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10301" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10351" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10352" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10353" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10354" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10355" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10404" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10405" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10406" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10407" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10408" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10409" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10458" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10459" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10460" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10462" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10511" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10512" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10513" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10514" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10516" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10564" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10565" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10566" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10567" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10568" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10617" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10618" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10619" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10620" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10621" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10622" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10670" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10671" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10672" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10673" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10674" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10675" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10723" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10724" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10725" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10726" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10727" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10728" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10776" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10777" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10778" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10779" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10780" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10781" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10829" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10830" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10831" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10832" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10833" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10834" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10882" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10883" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10884" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10885" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10886" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10887" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10935" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10936" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10937" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10939" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10940" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10989" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10990" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10991" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10992" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10993" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11042" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11043" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11044" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11045" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11046" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11095" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11096" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11097" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11098" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11148" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11149" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11150" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11151" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11152" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11199" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11200" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11201" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11202" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11203" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11204" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11252" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11253" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11254" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11255" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11256" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11257" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11305" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11306" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11307" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11308" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11309" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11310" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11358" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11359" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11360" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11361" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11362" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11363" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11411" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11412" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11413" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11414" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11415" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11416" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11464" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11466" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11469" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11517" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11518" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11519" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11521" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11522" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11570" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11572" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11575" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11676" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11677" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11679" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11729" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11730" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11731" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11732" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11733" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11782" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11783" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11784" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11785" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11786" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11787" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11835" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11836" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11837" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11838" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11840" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11888" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11889" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11890" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11891" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11892" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11941" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11942" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11943" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11944" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11945" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11946" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11994" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11995" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11996" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11997" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11998" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11999" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12047" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12048" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12049" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12050" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12051" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12052" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12100" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12101" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12102" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12103" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12104" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12153" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12154" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12155" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12156" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12157" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12158" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12206" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12207" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12208" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12209" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12210" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12211" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12259" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12260" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12261" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12262" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12263" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12264" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12312" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12313" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12314" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12315" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12316" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12317" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12365" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12366" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12367" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12368" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12369" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12370" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12418" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12419" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12420" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12421" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12422" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12423" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12471" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12472" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12473" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12474" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12475" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12476" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12524" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12525" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12526" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12527" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12528" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12529" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12577" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12578" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12579" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12580" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12582" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12630" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12631" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12632" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12633" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12634" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12683" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12684" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12685" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12686" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12687" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12688" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12736" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12737" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12738" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12739" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12740" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12741" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12789" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12790" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12791" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12792" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12793" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12794" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12842" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12843" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12844" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12845" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12846" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12847" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12895" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12896" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12897" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12899" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12900" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12948" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12949" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12950" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12951" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12953" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13002" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13003" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13004" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13005" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13065" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13066" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13067" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13068" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13069" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13119" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13120" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13172" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13173" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13224" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13225" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13226" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13227" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13228" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13277" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13278" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13279" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13280" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13281" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13282" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13339" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13340" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13341" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13342" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13343" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13401" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13402" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13403" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13404" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13405" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13406" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13463" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13464" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13465" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13467" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13468" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13522" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13523" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13524" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13525" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13526" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13527" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13581" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13582" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13583" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13584" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13585" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13586" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13635" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13636" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13637" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13638" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13639" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13640" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13689" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13690" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13691" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13692" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13693" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13694" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13743" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13744" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13745" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13746" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13747" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13748" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13797" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13798" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13799" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13800" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13801" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13802" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13851" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13852" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13853" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13854" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13855" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13905" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13906" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13907" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13908" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13910" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13959" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13960" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13961" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13962" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13964" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14013" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14014" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14015" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14016" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14018" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14067" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14068" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14069" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14070" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14071" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14072" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14122" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14123" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14124" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14175" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14176" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14177" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14178" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14180" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14229" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14230" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14231" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14232" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14234" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14283" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14284" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14285" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14286" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14288" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14337" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14338" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14339" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14340" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14341" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14342" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14391" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14392" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14393" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14394" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14395" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14396" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14444" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14445" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14446" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14447" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14448" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14449" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14497" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14498" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14499" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14500" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14501" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14502" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14550" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14551" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14552" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14553" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14554" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14555" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14603" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14604" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14605" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14606" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14607" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14608" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14656" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14657" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14658" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14659" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14660" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14661" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14710" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14711" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14712" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14713" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14714" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14715" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14763" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14764" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14765" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14766" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14767" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14768" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14816" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14817" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14818" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14819" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14820" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14821" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14869" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14870" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14871" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14872" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14873" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14874" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14922" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14923" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14924" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14925" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14926" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14927" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14975" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14976" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14977" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14978" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14979" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14980" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15029" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15030" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15031" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15032" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15033" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15034" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15083" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15084" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15085" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15086" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15087" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15088" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15138" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15139" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15191" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15192" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15193" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15194" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15195" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15196" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15245" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15246" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15247" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15248" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15249" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15250" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15299" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15300" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15301" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15302" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15303" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15304" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15353" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15354" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15355" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15356" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15357" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15358" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15407" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15408" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15409" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15410" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15411" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15412" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15461" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15462" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15463" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15464" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15465" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15466" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15515" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15516" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15517" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15518" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15519" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15520" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15569" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15570" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15571" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15572" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15573" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15574" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15623" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15624" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15625" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15626" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15627" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15628" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15677" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15678" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15679" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15680" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15681" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15682" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15731" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15732" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15733" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15734" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15735" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15736" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15785" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15786" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15787" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15788" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15789" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15790" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15839" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15840" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15841" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15842" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15843" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15844" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15893" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15894" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15895" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15896" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15897" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15947" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15948" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15949" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15950" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15951" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15952" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16001" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16002" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16003" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16004" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16005" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16006" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16055" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16056" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16057" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16058" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16059" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16060" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16109" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16110" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16111" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16112" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16114" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16163" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16164" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16165" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16217" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16218" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16219" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16220" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16221" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16222" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16271" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16272" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16273" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16274" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16275" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16276" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16325" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16326" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16327" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16328" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16329" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16330" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16379" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16380" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16381" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16382" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16383" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16384" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16432" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16433" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16434" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16435" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16436" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16437" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16485" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16486" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16487" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16488" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16489" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16490" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16538" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16539" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16540" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16541" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16542" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16543" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16591" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16592" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16593" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16594" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16595" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16596" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16644" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16645" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16646" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16647" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16648" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16649" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16697" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16698" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16699" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16700" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16701" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16702" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16750" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16751" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16752" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16753" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16754" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16755" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16803" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16804" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16805" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16806" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16807" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16808" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16856" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16857" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16858" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16859" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16860" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16861" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16909" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16910" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16911" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16912" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16913" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16914" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16963" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16964" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16965" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16966" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16967" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16968" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17017" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17018" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17019" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17020" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17021" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17022" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17071" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17072" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17073" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17074" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17075" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17076" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17126" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17127" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17129" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17130" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17179" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17180" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17181" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17182" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17183" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17184" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17233" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17234" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17235" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17236" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17237" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17238" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17287" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17288" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17289" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17290" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17291" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17292" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17341" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17342" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17343" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17344" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17345" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17346" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17395" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17396" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17397" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17398" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17399" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17400" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17449" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17450" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17451" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17452" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17453" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17454" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17503" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17504" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17505" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17506" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17507" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17508" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17557" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17558" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17559" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17560" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17561" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17562" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17611" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17612" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17613" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17614" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17615" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17616" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17665" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17666" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17667" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17668" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17669" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17670" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17719" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17720" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17721" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17722" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17723" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17724" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17773" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17774" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17775" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17776" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17777" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17778" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17826" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17827" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17828" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17829" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17830" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17831" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17880" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17881" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17882" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17883" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17884" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17885" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17934" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17935" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17936" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17937" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17938" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17939" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17988" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17989" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17990" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17991" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17992" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17993" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18041" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18042" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18043" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18044" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18045" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18046" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18094" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18095" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18096" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18097" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18098" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="27">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>

--- a/procurement_documents/IAR Template.xlsx
+++ b/procurement_documents/IAR Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\itrac\procurement_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1882B32E-5EC8-443C-B214-EA64B92EAF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F189163E-FD55-4883-80D1-84847093A9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6CD071E1-92CF-4D3E-842E-C4264179AD1A}"/>
   </bookViews>
@@ -606,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -769,161 +769,158 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1363,64 +1360,64 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="112" t="e" vm="1">
+      <c r="A2" s="95" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="109"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="100" t="s">
+      <c r="A3" s="96"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="109"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="101" t="s">
+      <c r="A4" s="96"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="74"/>
-      <c r="F4" s="75"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="109"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="79"/>
+      <c r="A5" s="96"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="103" t="s">
+      <c r="B6" s="97"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="113"/>
-      <c r="B7" s="114"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1442,7 +1439,7 @@
       <c r="E9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="118"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1484,11 +1481,11 @@
       <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
@@ -1497,186 +1494,186 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="116"/>
+      <c r="A14" s="68"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="23"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="116"/>
+      <c r="A15" s="68"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
       <c r="D15" s="25"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="116"/>
+      <c r="A16" s="68"/>
       <c r="B16" s="26"/>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
       <c r="H16" s="67"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="116"/>
+      <c r="A17" s="68"/>
       <c r="B17" s="29"/>
       <c r="C17" s="27"/>
       <c r="D17" s="28"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="116"/>
+      <c r="A18" s="68"/>
       <c r="B18" s="26"/>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="118"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="30"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="116"/>
+      <c r="A19" s="68"/>
       <c r="B19" s="31"/>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="118"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="30"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="117"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="118"/>
+      <c r="A20" s="69"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="30"/>
       <c r="I20" s="67"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="117"/>
+      <c r="A21" s="69"/>
       <c r="B21" s="33"/>
       <c r="C21" s="34"/>
       <c r="D21" s="35"/>
-      <c r="E21" s="118"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="30"/>
       <c r="K21" s="67"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="117"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="118"/>
+      <c r="A22" s="69"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="36"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="117"/>
+      <c r="A23" s="69"/>
       <c r="B23" s="26"/>
       <c r="C23" s="37"/>
       <c r="D23" s="38"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="116"/>
+      <c r="A24" s="68"/>
       <c r="B24" s="39"/>
       <c r="C24" s="40"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="116"/>
+      <c r="A25" s="68"/>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
       <c r="D25" s="38"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="116"/>
+      <c r="A26" s="68"/>
       <c r="B26" s="21"/>
       <c r="C26" s="34"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="116"/>
+      <c r="A27" s="68"/>
       <c r="B27" s="21"/>
       <c r="C27" s="34"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="118"/>
+      <c r="E27" s="70"/>
       <c r="F27" s="42"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="116"/>
+      <c r="A28" s="68"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="118"/>
+      <c r="E28" s="70"/>
       <c r="F28" s="42"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="116"/>
+      <c r="A29" s="68"/>
       <c r="B29" s="33"/>
       <c r="C29" s="43"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="118"/>
+      <c r="E29" s="70"/>
       <c r="F29" s="42"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="116"/>
+      <c r="A30" s="68"/>
       <c r="B30" s="33"/>
       <c r="C30" s="43"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="118"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="42"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="116"/>
+      <c r="A31" s="68"/>
       <c r="B31" s="21"/>
       <c r="C31" s="43"/>
       <c r="D31" s="38"/>
-      <c r="E31" s="118"/>
+      <c r="E31" s="70"/>
       <c r="F31" s="42"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="116"/>
+      <c r="A32" s="68"/>
       <c r="B32" s="33"/>
       <c r="C32" s="43"/>
       <c r="D32" s="44"/>
-      <c r="E32" s="118"/>
+      <c r="E32" s="70"/>
       <c r="F32" s="42"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="116"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="21"/>
       <c r="C33" s="34"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="118"/>
+      <c r="E33" s="70"/>
       <c r="F33" s="42"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="116"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="118"/>
+      <c r="A34" s="68"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="45"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="116"/>
+      <c r="A35" s="68"/>
       <c r="B35" s="46"/>
       <c r="C35" s="47"/>
       <c r="D35" s="48"/>
-      <c r="E35" s="118"/>
+      <c r="E35" s="70"/>
       <c r="F35" s="49"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="116"/>
+      <c r="A36" s="68"/>
       <c r="B36" s="50"/>
       <c r="C36" s="51"/>
       <c r="D36" s="52"/>
@@ -1684,47 +1681,47 @@
       <c r="F36" s="49"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="116"/>
+      <c r="A37" s="68"/>
       <c r="B37" s="54"/>
       <c r="C37" s="34"/>
       <c r="D37" s="52"/>
-      <c r="E37" s="118"/>
+      <c r="E37" s="70"/>
       <c r="F37" s="49"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="116"/>
+      <c r="A38" s="68"/>
       <c r="B38" s="55"/>
       <c r="C38" s="56"/>
       <c r="D38" s="23"/>
-      <c r="E38" s="118"/>
+      <c r="E38" s="70"/>
       <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="116"/>
+      <c r="A39" s="68"/>
       <c r="B39" s="21"/>
       <c r="C39" s="57"/>
       <c r="D39" s="52"/>
-      <c r="E39" s="118"/>
+      <c r="E39" s="70"/>
       <c r="F39" s="30"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="116"/>
+      <c r="A40" s="68"/>
       <c r="B40" s="58"/>
       <c r="C40" s="57"/>
       <c r="D40" s="52"/>
-      <c r="E40" s="118"/>
+      <c r="E40" s="70"/>
       <c r="F40" s="30"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="116"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="88"/>
-      <c r="D41" s="89"/>
+      <c r="A41" s="68"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="59"/>
       <c r="F41" s="60"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="116"/>
+      <c r="A42" s="68"/>
       <c r="B42" s="61"/>
       <c r="C42" s="57"/>
       <c r="D42" s="52"/>
@@ -1732,16 +1729,16 @@
       <c r="F42" s="60"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76" t="s">
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="62"/>
@@ -1772,11 +1769,11 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="93" t="s">
+      <c r="A47" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="94"/>
-      <c r="C47" s="95"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="77"/>
       <c r="D47" s="66" t="s">
         <v>25</v>
       </c>
@@ -1786,11 +1783,11 @@
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="93" t="s">
+      <c r="A48" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="94"/>
-      <c r="C48" s="95"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="77"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="s">
         <v>28</v>
@@ -1814,34 +1811,34 @@
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="97"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="97" t="s">
+      <c r="A51" s="78"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="97"/>
-      <c r="F51" s="98"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="80"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="93" t="s">
+      <c r="A52" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="94"/>
-      <c r="C52" s="95"/>
-      <c r="D52" s="94" t="s">
+      <c r="B52" s="76"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E52" s="94"/>
-      <c r="F52" s="95"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="77"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="90"/>
-      <c r="B53" s="91"/>
-      <c r="C53" s="92"/>
-      <c r="D53" s="91"/>
-      <c r="E53" s="91"/>
-      <c r="F53" s="92"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="74"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3971,14 +3968,6 @@
     <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D5:F5"/>
@@ -3995,6 +3984,14 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="B2:C5"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
@@ -4016,68 +4013,68 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="71" t="s">
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="73" t="s">
+      <c r="A4" s="112"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="74"/>
-      <c r="F4" s="75"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="79"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="80" t="s">
+      <c r="B6" s="112"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -4161,11 +4158,11 @@
       <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
@@ -4232,9 +4229,9 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="86"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="24"/>
       <c r="F20" s="30"/>
       <c r="I20" s="67"/>
@@ -4250,9 +4247,9 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="86"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="24"/>
       <c r="F22" s="36"/>
     </row>
@@ -4346,9 +4343,9 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="86"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="91"/>
       <c r="E34" s="24"/>
       <c r="F34" s="45"/>
     </row>
@@ -4402,9 +4399,9 @@
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="88"/>
-      <c r="D41" s="89"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="59"/>
       <c r="F41" s="60"/>
     </row>
@@ -4417,16 +4414,16 @@
       <c r="F42" s="60"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76" t="s">
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="62"/>
@@ -4461,11 +4458,11 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="93" t="s">
+      <c r="A47" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="94"/>
-      <c r="C47" s="95"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="77"/>
       <c r="D47" s="66" t="s">
         <v>25</v>
       </c>
@@ -4475,11 +4472,11 @@
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="93" t="s">
+      <c r="A48" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="94"/>
-      <c r="C48" s="95"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="77"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="s">
         <v>28</v>
@@ -4503,36 +4500,36 @@
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="96" t="s">
+      <c r="A51" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="97"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="97" t="s">
+      <c r="B51" s="79"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="97"/>
-      <c r="F51" s="98"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="80"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="93" t="s">
+      <c r="A52" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="94"/>
-      <c r="C52" s="95"/>
-      <c r="D52" s="94" t="s">
+      <c r="B52" s="76"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E52" s="94"/>
-      <c r="F52" s="95"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="77"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="90"/>
-      <c r="B53" s="91"/>
-      <c r="C53" s="92"/>
-      <c r="D53" s="91"/>
-      <c r="E53" s="91"/>
-      <c r="F53" s="92"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="74"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6662,14 +6659,12 @@
     <row r="18099" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A5:C5"/>
@@ -6683,12 +6678,14 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
